--- a/src/test/resources/testData.xlsx
+++ b/src/test/resources/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumreen\IdeaProjects\saucedemo-selenium-java-framework\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C997EAB-A475-4C22-BFB4-B6166D952738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE6EEA3-1FF6-429F-AFDE-963878ACF133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{54D39150-26B2-44CE-95A6-9D876FBA1E81}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>Username</t>
   </si>
@@ -64,6 +64,15 @@
   </si>
   <si>
     <t>Epic sadface: Sorry, this user has been locked out.</t>
+  </si>
+  <si>
+    <t>Epic sadface: Username and password do not match any user in this service</t>
+  </si>
+  <si>
+    <t>hghghmgjmhjmhj,ghmfggcg</t>
+  </si>
+  <si>
+    <t>invalid</t>
   </si>
 </sst>
 </file>
@@ -474,7 +483,7 @@
       <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -506,9 +515,19 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+    <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B6" s="2"/>

--- a/src/test/resources/testData.xlsx
+++ b/src/test/resources/testData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumreen\IdeaProjects\saucedemo-selenium-java-framework\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE6EEA3-1FF6-429F-AFDE-963878ACF133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D982E545-3113-4F2B-9B3F-BBF1F874DBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{54D39150-26B2-44CE-95A6-9D876FBA1E81}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>Username</t>
   </si>
@@ -69,17 +69,23 @@
     <t>Epic sadface: Username and password do not match any user in this service</t>
   </si>
   <si>
-    <t>hghghmgjmhjmhj,ghmfggcg</t>
-  </si>
-  <si>
     <t>invalid</t>
+  </si>
+  <si>
+    <t>hghghmgjmhjmhjghmfggcg</t>
+  </si>
+  <si>
+    <t>standard123</t>
+  </si>
+  <si>
+    <t>1234@$</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,16 +106,37 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -117,27 +144,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -450,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3280A15-BBB5-477F-883D-2173EF5D19BD}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
@@ -460,79 +516,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="5">
         <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B6" s="2"/>
+    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{E7E6B0B3-BD3F-43C0-9FB3-4A7F4E624E2D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>